--- a/TestData/T2215_ImportPositionsWithTeamMembers.xlsx
+++ b/TestData/T2215_ImportPositionsWithTeamMembers.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20394"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sgoyal0427\source\repos\SF_Automation\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SGoyal0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06A03B76-5E63-4AE7-BEB0-D826BE82AA03}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1442FEE7-9782-4375-BE70-0A741254D374}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="7170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -53,9 +53,6 @@
     <t>BUS - Business Services</t>
   </si>
   <si>
-    <t>Dealership &amp; Rental Services</t>
-  </si>
-  <si>
     <t>No</t>
   </si>
   <si>
@@ -240,6 +237,9 @@
   </si>
   <si>
     <t>100000.0</t>
+  </si>
+  <si>
+    <t>CSDN-0000001546</t>
   </si>
 </sst>
 </file>
@@ -286,12 +286,14 @@
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -573,34 +575,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AB2"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="8.85546875" style="2"/>
-    <col min="3" max="3" width="20.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.85546875" style="2"/>
-    <col min="15" max="17" width="14.5703125" style="5" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="16.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5703125" style="5" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="21" style="2" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="27" style="2" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="8.85546875" style="2"/>
-    <col min="26" max="26" width="20.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="8.85546875" style="2"/>
+    <col min="3" max="3" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="14.5546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="21" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="27" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="20.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -623,153 +621,153 @@
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="J1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>14</v>
-      </c>
       <c r="L1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="M1" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="N1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="O1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="P1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="Q1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="R1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="S1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="T1" s="3" t="s">
+      <c r="T1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="U1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="U1" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="V1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="W1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="W1" s="1" t="s">
-        <v>32</v>
-      </c>
       <c r="X1" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Y1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Z1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="AB1" s="1" t="s">
-        <v>41</v>
-      </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>66</v>
+    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B2" t="s">
+        <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D2" t="s">
         <v>7</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F2" t="s">
         <v>8</v>
       </c>
-      <c r="F2" t="s">
-        <v>9</v>
-      </c>
       <c r="G2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="M2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N2" t="s">
+        <v>66</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="R2" t="s">
+        <v>26</v>
+      </c>
+      <c r="S2" t="s">
+        <v>26</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="U2" t="s">
+        <v>29</v>
+      </c>
+      <c r="V2" t="s">
+        <v>68</v>
+      </c>
+      <c r="W2" t="s">
+        <v>32</v>
+      </c>
+      <c r="X2" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y2" t="s">
         <v>67</v>
       </c>
-      <c r="O2" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="P2" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q2" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="R2" t="s">
-        <v>27</v>
-      </c>
-      <c r="S2" t="s">
-        <v>27</v>
-      </c>
-      <c r="T2" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="U2" t="s">
-        <v>30</v>
-      </c>
-      <c r="V2" t="s">
+      <c r="Z2" t="s">
+        <v>63</v>
+      </c>
+      <c r="AA2" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="W2" t="s">
-        <v>33</v>
-      </c>
-      <c r="X2" t="s">
+      <c r="AB2" s="3" t="s">
         <v>35</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>68</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>64</v>
-      </c>
-      <c r="AA2" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="AB2" s="4" t="s">
-        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -781,26 +779,26 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>21</v>
-      </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -811,98 +809,98 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:M2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="26.28515625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="26.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>53</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>54</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H2" t="s">
+        <v>57</v>
+      </c>
+      <c r="I2" t="s">
+        <v>58</v>
+      </c>
+      <c r="J2" t="s">
+        <v>59</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="L2" t="s">
+        <v>42</v>
+      </c>
+      <c r="M2" t="s">
         <v>62</v>
-      </c>
-      <c r="C2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="H2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I2" t="s">
-        <v>59</v>
-      </c>
-      <c r="J2" t="s">
-        <v>60</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="L2" t="s">
-        <v>43</v>
-      </c>
-      <c r="M2" t="s">
-        <v>63</v>
       </c>
     </row>
   </sheetData>
